--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2421,6 +2421,29 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>544353643</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1979467</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>The Best $1000 Gaming PC Build for 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,35 @@
       </c>
       <c r="G2" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>383887</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76777589</v>
+      </c>
+      <c r="E3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bro had a brilliant idea #pcbuild #pcgaming #pc #gamingpc</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Avg_Views_Top200_Last30d</t>
+          <t>New_Uploads_Last7d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -508,6 +508,21 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>525</v>
       </c>
     </row>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,21 @@
       </c>
       <c r="C4" t="n">
         <v>525</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,21 @@
       </c>
       <c r="C5" t="n">
         <v>425</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,21 @@
         <v>275</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +571,21 @@
         <v>14</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,21 @@
         <v>125</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,21 @@
         <v>163</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,6 +631,21 @@
         <v>543</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>361</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +646,21 @@
         <v>361</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,6 +661,21 @@
         <v>160</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,6 +676,21 @@
         <v>539</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,6 +691,21 @@
         <v>225</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,21 @@
         <v>375</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,21 @@
         <v>325</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +736,21 @@
         <v>25</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,6 +751,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,6 +766,21 @@
         <v>275</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>552</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,21 @@
         <v>552</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,21 @@
         <v>175</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>549</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,6 +811,21 @@
         <v>549</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,6 +826,21 @@
         <v>257</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,6 +841,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,6 +856,21 @@
         <v>175</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,6 +871,21 @@
         <v>225</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,6 +886,21 @@
         <v>175</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,21 @@
         <v>275</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>475</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,21 @@
         <v>475</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,21 @@
         <v>548</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,21 @@
         <v>525</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>458</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,6 +961,21 @@
         <v>458</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +976,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,6 +991,21 @@
         <v>25</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,21 @@
         <v>556</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>546</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,21 @@
         <v>546</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,21 @@
         <v>110</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,6 +1051,21 @@
         <v>548</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,6 +1066,21 @@
         <v>308</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>358</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,21 @@
         <v>358</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,21 @@
         <v>542</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>545</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,21 @@
         <v>545</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,21 @@
         <v>536</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,21 @@
         <v>543</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,6 +1156,21 @@
         <v>519</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>541</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,6 +1171,21 @@
         <v>541</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,21 @@
         <v>550</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,6 +1201,21 @@
         <v>531</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,6 +1216,21 @@
         <v>539</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>530</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1231,21 @@
         <v>530</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1246,21 @@
         <v>533</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1261,6 +1261,21 @@
         <v>548</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>530</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,6 +1276,21 @@
         <v>530</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,21 @@
         <v>533</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,21 @@
         <v>542</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,6 +1321,21 @@
         <v>544</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,6 +1336,21 @@
         <v>551</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,6 +1351,21 @@
         <v>540</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>541</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,6 +1366,21 @@
         <v>541</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1381,6 +1381,21 @@
         <v>531</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>547</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,21 @@
         <v>547</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,6 +1411,21 @@
         <v>550</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>558</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,6 +1426,21 @@
         <v>558</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,6 +1441,21 @@
         <v>528</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,21 @@
         <v>531</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1471,21 @@
         <v>542</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>554</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +1486,21 @@
         <v>554</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,6 +1501,21 @@
         <v>544</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,21 @@
         <v>488</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,6 +1531,21 @@
         <v>536</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>520</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,6 +1546,21 @@
         <v>520</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,6 +1561,21 @@
         <v>544</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1576,6 +1576,21 @@
         <v>542</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>538</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1591,6 +1591,21 @@
         <v>538</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +1606,21 @@
         <v>536</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,6 +1621,21 @@
         <v>536</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,6 +1636,21 @@
         <v>537</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,6 +1651,21 @@
         <v>528</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,6 +1666,21 @@
         <v>540</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>541</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,21 @@
         <v>541</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1696,6 +1696,21 @@
         <v>543</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,6 +1711,21 @@
         <v>535</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,21 @@
         <v>544</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>529</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,21 @@
         <v>529</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,6 +1756,21 @@
         <v>539</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,6 +1771,21 @@
         <v>542</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>538</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +1786,21 @@
         <v>538</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,6 +1801,21 @@
         <v>500</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,6 +1816,21 @@
         <v>500</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,6 +1831,21 @@
         <v>400</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1846,6 +1846,21 @@
         <v>500</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,21 @@
         <v>54</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,6 +1876,21 @@
         <v>500</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,6 +1891,21 @@
         <v>350</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>541</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1906,6 +1906,21 @@
         <v>541</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,6 +1921,21 @@
         <v>159</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1936,6 +1936,21 @@
         <v>112</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,6 +1951,21 @@
         <v>533</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1966,6 +1966,21 @@
         <v>400</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>545</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,6 +1981,21 @@
         <v>545</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,6 +1996,21 @@
         <v>531</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +2011,21 @@
         <v>537</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,6 +2026,21 @@
         <v>544</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,6 +2041,21 @@
         <v>551</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2056,6 +2056,21 @@
         <v>150</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>530</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,6 +2071,21 @@
         <v>530</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2086,6 +2086,21 @@
         <v>535</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,6 +2101,21 @@
         <v>539</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2116,6 +2116,21 @@
         <v>424</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/youtube_diy_sentiment.xlsx
+++ b/data/youtube_diy_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2131,6 +2131,21 @@
         <v>535</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Gaming PC Build</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
